--- a/tests/SAMPLE_Lenovo_Inventory_RICH_LO.xlsx
+++ b/tests/SAMPLE_Lenovo_Inventory_RICH_LO.xlsx
@@ -169,7 +169,7 @@
     <t xml:space="preserve">SGM546M66</t>
   </si>
   <si>
-    <t xml:space="preserve">St. Vincent Ferrer Academy</t>
+    <t xml:space="preserve">Sample Ferrer Academy</t>
   </si>
   <si>
     <t xml:space="preserve">1400156415</t>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">PF4HNXKZ0</t>
   </si>
   <si>
-    <t xml:space="preserve">Corpus Christi College</t>
+    <t xml:space="preserve">Sample Christi College</t>
   </si>
   <si>
     <t xml:space="preserve">1400177806</t>
@@ -259,7 +259,7 @@
     <t xml:space="preserve">PF4D4Q3E1</t>
   </si>
   <si>
-    <t xml:space="preserve">San Isidro Integrated School</t>
+    <t xml:space="preserve">Sample Integrated School</t>
   </si>
   <si>
     <t xml:space="preserve">1400188021</t>
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Mark Villanueva</t>
   </si>
   <si>
-    <t xml:space="preserve">12 Narra Lane, Pasig</t>
+    <t xml:space="preserve">12 Sample Lane, Sample City</t>
   </si>
   <si>
     <t xml:space="preserve">+63 920 444 5566</t>

--- a/tests/SAMPLE_Lenovo_Inventory_RICH_LO.xlsx
+++ b/tests/SAMPLE_Lenovo_Inventory_RICH_LO.xlsx
@@ -169,7 +169,7 @@
     <t xml:space="preserve">SGM546M66</t>
   </si>
   <si>
-    <t xml:space="preserve">St. Vincent Ferrer Academy</t>
+    <t xml:space="preserve">Sample Ferrer Academy</t>
   </si>
   <si>
     <t xml:space="preserve">1400156415</t>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">PF4HNXKZ0</t>
   </si>
   <si>
-    <t xml:space="preserve">Corpus Christi College</t>
+    <t xml:space="preserve">Sample Christi College</t>
   </si>
   <si>
     <t xml:space="preserve">1400177806</t>
@@ -259,7 +259,7 @@
     <t xml:space="preserve">PF4D4Q3E1</t>
   </si>
   <si>
-    <t xml:space="preserve">Silver Isle Integrated School</t>
+    <t xml:space="preserve">Sample Integrated School</t>
   </si>
   <si>
     <t xml:space="preserve">1400188021</t>
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Mark Villanueva</t>
   </si>
   <si>
-    <t xml:space="preserve">12 Narra Lane, Pasig</t>
+    <t xml:space="preserve">12 Sample Lane, Sample City</t>
   </si>
   <si>
     <t xml:space="preserve">+63 920 444 5566</t>
